--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260628_205302.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
